--- a/resources/master_song_links.xlsx
+++ b/resources/master_song_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D07BB3D-A9EA-7D49-93F4-10C270DA975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F74B3E4C-2C85-4C49-AE2D-4E1A74AED22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="144">
   <si>
     <t>KINGS OF EWING — SONG TRACKER MASTER LINKS</t>
   </si>
@@ -449,13 +449,16 @@
   </si>
   <si>
     <t>https://www.kingsofewing.com/docs/music/for_what_its_worth.pdf</t>
+  </si>
+  <si>
+    <t>https://www.kingsofewing.com/docs/music/just_what_i_needed.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -483,16 +486,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Courier New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Courier New"/>
-      <family val="1"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color rgb="FF0563C1"/>
@@ -500,8 +493,15 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Courier New"/>
       <family val="1"/>
     </font>
@@ -601,64 +601,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -998,26 +1005,28 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.33203125" style="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="72" customWidth="1"/>
     <col min="5" max="5" width="139.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="21" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" s="7" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-    </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+    </row>
+    <row r="2" spans="1:5" s="23" customFormat="1" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="22" t="s">
@@ -1027,788 +1036,790 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:5" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="10" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="B5" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="6" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="9" t="s">
+      <c r="B6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="B7" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="9" t="s">
+      <c r="B8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="6" t="s">
+      <c r="B9" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="9" t="s">
+      <c r="B10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="B11" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="10" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="12" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="9" t="s">
+      <c r="B12" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="6" t="s">
+      <c r="B13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
+    <row r="15" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="B15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="9" t="s">
+      <c r="B16" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="11" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
+    <row r="17" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="B17" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="10" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="9" t="s">
+      <c r="B18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="11" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
+    <row r="19" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="B19" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
+    <row r="20" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="9" t="s">
+      <c r="B20" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="6" t="s">
+      <c r="B21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="22" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="9" t="s">
+      <c r="B22" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+    <row r="23" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
+      <c r="B23" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="9" t="s">
+      <c r="B24" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="10" t="s">
+      <c r="E24" s="11"/>
+    </row>
+    <row r="25" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="B25" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="10" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="9" t="s">
+      <c r="B26" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="10" t="s">
+    <row r="27" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="B27" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="10" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="9" t="s">
+      <c r="B28" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="11" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="10" t="s">
+    <row r="29" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="B29" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="10" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="9" t="s">
+      <c r="B30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="11" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="10" t="s">
+    <row r="31" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="6" t="s">
+      <c r="B31" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="9" t="s">
+      <c r="B32" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="9" t="s">
+      <c r="E32" s="11" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
+    <row r="33" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="6" t="s">
+      <c r="B33" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="10" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+    <row r="34" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="9" t="s">
+      <c r="B34" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E34" s="9" t="s">
+      <c r="E34" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="10" t="s">
+    <row r="35" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="6" t="s">
+      <c r="B35" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="10" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="9" t="s">
+      <c r="B36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="11" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="10" t="s">
+    <row r="37" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="6" t="s">
+      <c r="B37" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="10" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="9" t="s">
+      <c r="B38" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="11" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+    <row r="39" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="6" t="s">
+      <c r="B39" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="10" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="9" t="s">
+      <c r="B40" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="11" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="6" t="s">
+      <c r="B41" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="10" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="B42" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="11" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+    <row r="43" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="6" t="s">
+      <c r="B43" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="10" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7" t="s">
+    <row r="44" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B44" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="9" t="s">
+      <c r="B44" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E44" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
+    <row r="45" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="6" t="s">
+      <c r="B45" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="7" t="s">
+    <row r="46" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="9" t="s">
+      <c r="B46" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="E46" s="9" t="s">
+      <c r="E46" s="11" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-    </row>
-    <row r="48" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="7" t="s">
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+    </row>
+    <row r="48" spans="1:5" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B48" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="9" t="s">
+      <c r="B48" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="E48" s="9" t="s">
+      <c r="E48" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="16" t="s">
+    <row r="49" spans="1:5" ht="17" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B49" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="18" t="s">
+      <c r="B49" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E49" s="9" t="s">
+      <c r="E49" s="11" t="s">
         <v>138</v>
       </c>
     </row>
